--- a/FresherAndroid/Schedule/HN26_FR_Android_02_TrainingCalendar_version_1.0.xlsx
+++ b/FresherAndroid/Schedule/HN26_FR_Android_02_TrainingCalendar_version_1.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\FresherAndroid\Schedule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9C899D-21F4-4CA8-9E34-059A6582E8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A5DAF3-BD7C-4AA9-8ABA-DBD6BD796B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1829,7 +1829,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1938,10 +1938,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="15">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3036,10 +3039,10 @@
       <c r="F8" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="37" t="s">
         <v>28</v>
       </c>
       <c r="I8" s="31"/>
@@ -3070,10 +3073,10 @@
       <c r="F9" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="37" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="31"/>
@@ -3159,10 +3162,10 @@
       <c r="F13" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="35" t="s">
+      <c r="G13" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="35" t="s">
+      <c r="H13" s="37" t="s">
         <v>45</v>
       </c>
       <c r="I13" s="31"/>
@@ -3193,10 +3196,10 @@
       <c r="F14" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="35" t="s">
+      <c r="G14" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="35" t="s">
+      <c r="H14" s="37" t="s">
         <v>45</v>
       </c>
       <c r="I14" s="31"/>
@@ -3225,10 +3228,10 @@
       <c r="F15" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="35" t="s">
+      <c r="H15" s="37" t="s">
         <v>45</v>
       </c>
       <c r="I15" s="31"/>
@@ -3286,10 +3289,10 @@
       <c r="F18" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H18" s="35" t="s">
+      <c r="H18" s="37" t="s">
         <v>62</v>
       </c>
       <c r="I18" s="31"/>
@@ -3320,10 +3323,10 @@
       <c r="F19" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="35" t="s">
+      <c r="G19" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H19" s="35" t="s">
+      <c r="H19" s="37" t="s">
         <v>62</v>
       </c>
       <c r="I19" s="31"/>
@@ -3354,14 +3357,14 @@
       <c r="F20" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="H20" s="35" t="s">
+      <c r="H20" s="37" t="s">
         <v>59</v>
       </c>
       <c r="I20" s="31"/>
-      <c r="J20" s="36" t="s">
+      <c r="J20" s="35" t="s">
         <v>473</v>
       </c>
       <c r="K20" s="31"/>
@@ -3388,10 +3391,10 @@
       <c r="F21" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="35" t="s">
+      <c r="G21" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="H21" s="35" t="s">
+      <c r="H21" s="37" t="s">
         <v>59</v>
       </c>
       <c r="I21" s="31"/>
@@ -3420,10 +3423,10 @@
       <c r="F22" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="H22" s="35" t="s">
+      <c r="H22" s="37" t="s">
         <v>59</v>
       </c>
       <c r="I22" s="31"/>
@@ -3481,10 +3484,10 @@
       <c r="F25" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G25" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="H25" s="35" t="s">
+      <c r="H25" s="37" t="s">
         <v>73</v>
       </c>
       <c r="I25" s="31"/>
@@ -3515,10 +3518,10 @@
       <c r="F26" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="35" t="s">
+      <c r="G26" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="H26" s="35" t="s">
+      <c r="H26" s="37" t="s">
         <v>73</v>
       </c>
       <c r="I26" s="31"/>
@@ -3549,10 +3552,10 @@
       <c r="F27" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G27" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="H27" s="35" t="s">
+      <c r="H27" s="37" t="s">
         <v>73</v>
       </c>
       <c r="I27" s="31"/>
@@ -3583,10 +3586,10 @@
       <c r="F28" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="35" t="s">
+      <c r="G28" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="37" t="s">
         <v>73</v>
       </c>
       <c r="I28" s="31"/>
@@ -3615,10 +3618,10 @@
       <c r="F29" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="H29" s="35" t="s">
+      <c r="H29" s="37" t="s">
         <v>73</v>
       </c>
       <c r="I29" s="31"/>
@@ -3678,10 +3681,10 @@
       <c r="F32" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G32" s="35" t="s">
+      <c r="G32" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="35" t="s">
+      <c r="H32" s="37" t="s">
         <v>82</v>
       </c>
       <c r="I32" s="31"/>
@@ -3712,10 +3715,10 @@
       <c r="F33" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="35" t="s">
+      <c r="G33" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="H33" s="35" t="s">
+      <c r="H33" s="37" t="s">
         <v>82</v>
       </c>
       <c r="I33" s="31"/>
@@ -3744,10 +3747,10 @@
       <c r="F34" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G34" s="35" t="s">
+      <c r="G34" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="H34" s="35" t="s">
+      <c r="H34" s="37" t="s">
         <v>82</v>
       </c>
       <c r="I34" s="31"/>
@@ -3776,10 +3779,10 @@
       <c r="F35" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G35" s="35" t="s">
+      <c r="G35" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="H35" s="35" t="s">
+      <c r="H35" s="37" t="s">
         <v>82</v>
       </c>
       <c r="I35" s="31"/>
@@ -3810,10 +3813,10 @@
       <c r="F36" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="35" t="s">
+      <c r="G36" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="H36" s="35" t="s">
+      <c r="H36" s="37" t="s">
         <v>82</v>
       </c>
       <c r="I36" s="31"/>
@@ -3844,10 +3847,10 @@
       <c r="F37" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G37" s="35" t="s">
+      <c r="G37" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="H37" s="35" t="s">
+      <c r="H37" s="37" t="s">
         <v>82</v>
       </c>
       <c r="I37" s="31"/>
@@ -3878,10 +3881,10 @@
       <c r="F38" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="35" t="s">
+      <c r="G38" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="H38" s="35" t="s">
+      <c r="H38" s="37" t="s">
         <v>82</v>
       </c>
       <c r="I38" s="31"/>
@@ -3910,10 +3913,10 @@
       <c r="F39" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G39" s="35" t="s">
+      <c r="G39" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="H39" s="35" t="s">
+      <c r="H39" s="37" t="s">
         <v>82</v>
       </c>
       <c r="I39" s="31"/>
@@ -3973,10 +3976,10 @@
       <c r="F42" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G42" s="35" t="s">
+      <c r="G42" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H42" s="35" t="s">
+      <c r="H42" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I42" s="31"/>
@@ -4007,10 +4010,10 @@
       <c r="F43" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="35" t="s">
+      <c r="G43" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H43" s="35" t="s">
+      <c r="H43" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I43" s="31"/>
@@ -4039,10 +4042,10 @@
       <c r="F44" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G44" s="35" t="s">
+      <c r="G44" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H44" s="35" t="s">
+      <c r="H44" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I44" s="31"/>
@@ -4071,10 +4074,10 @@
       <c r="F45" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G45" s="35" t="s">
+      <c r="G45" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H45" s="35" t="s">
+      <c r="H45" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I45" s="31"/>
@@ -4105,10 +4108,10 @@
       <c r="F46" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="35" t="s">
+      <c r="G46" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H46" s="35" t="s">
+      <c r="H46" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I46" s="31"/>
@@ -4139,10 +4142,10 @@
       <c r="F47" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G47" s="35" t="s">
+      <c r="G47" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H47" s="35" t="s">
+      <c r="H47" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I47" s="31"/>
@@ -4173,10 +4176,10 @@
       <c r="F48" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="35" t="s">
+      <c r="G48" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H48" s="35" t="s">
+      <c r="H48" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I48" s="31"/>
@@ -4205,10 +4208,10 @@
       <c r="F49" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G49" s="35" t="s">
+      <c r="G49" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H49" s="35" t="s">
+      <c r="H49" s="37" t="s">
         <v>89</v>
       </c>
       <c r="I49" s="31"/>
@@ -4268,10 +4271,10 @@
       <c r="F52" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G52" s="35" t="s">
+      <c r="G52" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="H52" s="35" t="s">
+      <c r="H52" s="37" t="s">
         <v>96</v>
       </c>
       <c r="I52" s="31"/>
@@ -4302,10 +4305,10 @@
       <c r="F53" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="35" t="s">
+      <c r="G53" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="H53" s="35" t="s">
+      <c r="H53" s="37" t="s">
         <v>96</v>
       </c>
       <c r="I53" s="31"/>
@@ -4334,10 +4337,10 @@
       <c r="F54" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G54" s="35" t="s">
+      <c r="G54" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="H54" s="35" t="s">
+      <c r="H54" s="37" t="s">
         <v>96</v>
       </c>
       <c r="I54" s="31"/>
@@ -4366,10 +4369,10 @@
       <c r="F55" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G55" s="35" t="s">
+      <c r="G55" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="H55" s="35" t="s">
+      <c r="H55" s="37" t="s">
         <v>96</v>
       </c>
       <c r="I55" s="31"/>
@@ -4400,10 +4403,10 @@
       <c r="F56" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="35" t="s">
+      <c r="G56" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="H56" s="35" t="s">
+      <c r="H56" s="37" t="s">
         <v>96</v>
       </c>
       <c r="I56" s="31"/>
@@ -4434,10 +4437,10 @@
       <c r="F57" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G57" s="35" t="s">
+      <c r="G57" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="H57" s="35" t="s">
+      <c r="H57" s="37" t="s">
         <v>96</v>
       </c>
       <c r="I57" s="31"/>
@@ -4468,10 +4471,10 @@
       <c r="F58" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G58" s="35" t="s">
+      <c r="G58" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="H58" s="35" t="s">
+      <c r="H58" s="37" t="s">
         <v>96</v>
       </c>
       <c r="I58" s="31"/>
@@ -4500,10 +4503,10 @@
       <c r="F59" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G59" s="35" t="s">
+      <c r="G59" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="H59" s="35" t="s">
+      <c r="H59" s="37" t="s">
         <v>96</v>
       </c>
       <c r="I59" s="31"/>
@@ -4563,10 +4566,10 @@
       <c r="F62" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G62" s="35" t="s">
+      <c r="G62" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H62" s="35" t="s">
+      <c r="H62" s="37" t="s">
         <v>103</v>
       </c>
       <c r="I62" s="31"/>
@@ -4597,10 +4600,10 @@
       <c r="F63" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G63" s="35" t="s">
+      <c r="G63" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H63" s="35" t="s">
+      <c r="H63" s="37" t="s">
         <v>103</v>
       </c>
       <c r="I63" s="31"/>
@@ -4629,10 +4632,10 @@
       <c r="F64" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G64" s="35" t="s">
+      <c r="G64" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H64" s="35" t="s">
+      <c r="H64" s="37" t="s">
         <v>103</v>
       </c>
       <c r="I64" s="31"/>
@@ -4661,10 +4664,10 @@
       <c r="F65" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G65" s="35" t="s">
+      <c r="G65" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H65" s="35" t="s">
+      <c r="H65" s="37" t="s">
         <v>103</v>
       </c>
       <c r="I65" s="31"/>
@@ -4695,10 +4698,10 @@
       <c r="F66" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G66" s="35" t="s">
+      <c r="G66" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H66" s="35" t="s">
+      <c r="H66" s="37" t="s">
         <v>103</v>
       </c>
       <c r="I66" s="31"/>
@@ -4729,10 +4732,10 @@
       <c r="F67" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G67" s="35" t="s">
+      <c r="G67" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H67" s="35" t="s">
+      <c r="H67" s="37" t="s">
         <v>103</v>
       </c>
       <c r="I67" s="31"/>
@@ -4792,10 +4795,10 @@
       <c r="F70" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G70" s="35" t="s">
+      <c r="G70" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="H70" s="35" t="s">
+      <c r="H70" s="37" t="s">
         <v>110</v>
       </c>
       <c r="I70" s="31"/>
@@ -4826,10 +4829,10 @@
       <c r="F71" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="G71" s="35" t="s">
+      <c r="G71" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="H71" s="35" t="s">
+      <c r="H71" s="37" t="s">
         <v>110</v>
       </c>
       <c r="I71" s="31"/>
@@ -4914,10 +4917,10 @@
       <c r="F74" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G74" s="35" t="s">
+      <c r="G74" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="H74" s="35" t="s">
+      <c r="H74" s="37" t="s">
         <v>120</v>
       </c>
       <c r="I74" s="31"/>
@@ -4946,10 +4949,10 @@
       <c r="F75" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G75" s="35" t="s">
+      <c r="G75" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="H75" s="35" t="s">
+      <c r="H75" s="37" t="s">
         <v>120</v>
       </c>
       <c r="I75" s="31"/>
@@ -4980,10 +4983,10 @@
       <c r="F76" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G76" s="35" t="s">
+      <c r="G76" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="H76" s="35" t="s">
+      <c r="H76" s="37" t="s">
         <v>120</v>
       </c>
       <c r="I76" s="31"/>
@@ -5041,10 +5044,10 @@
       <c r="F79" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G79" s="35" t="s">
+      <c r="G79" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="H79" s="35" t="s">
+      <c r="H79" s="37" t="s">
         <v>126</v>
       </c>
       <c r="I79" s="31"/>
@@ -5075,10 +5078,10 @@
       <c r="F80" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G80" s="35" t="s">
+      <c r="G80" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="H80" s="35" t="s">
+      <c r="H80" s="37" t="s">
         <v>126</v>
       </c>
       <c r="I80" s="31"/>
@@ -5109,10 +5112,10 @@
       <c r="F81" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G81" s="35" t="s">
+      <c r="G81" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="H81" s="35" t="s">
+      <c r="H81" s="37" t="s">
         <v>126</v>
       </c>
       <c r="I81" s="31"/>
@@ -5141,10 +5144,10 @@
       <c r="F82" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G82" s="35" t="s">
+      <c r="G82" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="H82" s="35" t="s">
+      <c r="H82" s="37" t="s">
         <v>126</v>
       </c>
       <c r="I82" s="31"/>
@@ -5175,10 +5178,10 @@
       <c r="F83" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G83" s="35" t="s">
+      <c r="G83" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="H83" s="35" t="s">
+      <c r="H83" s="37" t="s">
         <v>126</v>
       </c>
       <c r="I83" s="31"/>
@@ -5238,10 +5241,10 @@
       <c r="F86" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G86" s="35" t="s">
+      <c r="G86" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="H86" s="35" t="s">
+      <c r="H86" s="37" t="s">
         <v>133</v>
       </c>
       <c r="I86" s="31"/>
@@ -5270,10 +5273,10 @@
       <c r="F87" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G87" s="35" t="s">
+      <c r="G87" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="H87" s="35" t="s">
+      <c r="H87" s="37" t="s">
         <v>133</v>
       </c>
       <c r="I87" s="31"/>
@@ -5304,10 +5307,10 @@
       <c r="F88" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G88" s="35" t="s">
+      <c r="G88" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="H88" s="35" t="s">
+      <c r="H88" s="37" t="s">
         <v>133</v>
       </c>
       <c r="I88" s="31"/>
@@ -5336,10 +5339,10 @@
       <c r="F89" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G89" s="35" t="s">
+      <c r="G89" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="H89" s="35" t="s">
+      <c r="H89" s="37" t="s">
         <v>133</v>
       </c>
       <c r="I89" s="31"/>
@@ -5370,10 +5373,10 @@
       <c r="F90" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G90" s="35" t="s">
+      <c r="G90" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="H90" s="35" t="s">
+      <c r="H90" s="37" t="s">
         <v>133</v>
       </c>
       <c r="I90" s="31"/>
@@ -5404,10 +5407,10 @@
       <c r="F91" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G91" s="35" t="s">
+      <c r="G91" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="H91" s="35" t="s">
+      <c r="H91" s="37" t="s">
         <v>133</v>
       </c>
       <c r="I91" s="31"/>
@@ -5436,10 +5439,10 @@
       <c r="F92" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G92" s="35" t="s">
+      <c r="G92" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="H92" s="35" t="s">
+      <c r="H92" s="37" t="s">
         <v>133</v>
       </c>
       <c r="I92" s="31"/>
@@ -5470,10 +5473,10 @@
       <c r="F93" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G93" s="35" t="s">
+      <c r="G93" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="H93" s="35" t="s">
+      <c r="H93" s="37" t="s">
         <v>133</v>
       </c>
       <c r="I93" s="31"/>
@@ -5533,10 +5536,10 @@
       <c r="F96" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G96" s="35" t="s">
+      <c r="G96" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="H96" s="35" t="s">
+      <c r="H96" s="37" t="s">
         <v>140</v>
       </c>
       <c r="I96" s="31"/>
@@ -5565,10 +5568,10 @@
       <c r="F97" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G97" s="35" t="s">
+      <c r="G97" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="H97" s="35" t="s">
+      <c r="H97" s="37" t="s">
         <v>140</v>
       </c>
       <c r="I97" s="31"/>
@@ -5599,10 +5602,10 @@
       <c r="F98" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G98" s="35" t="s">
+      <c r="G98" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="H98" s="35" t="s">
+      <c r="H98" s="37" t="s">
         <v>140</v>
       </c>
       <c r="I98" s="31"/>
@@ -5631,10 +5634,10 @@
       <c r="F99" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G99" s="35" t="s">
+      <c r="G99" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="H99" s="35" t="s">
+      <c r="H99" s="37" t="s">
         <v>140</v>
       </c>
       <c r="I99" s="31"/>
@@ -5665,10 +5668,10 @@
       <c r="F100" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G100" s="35" t="s">
+      <c r="G100" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="H100" s="35" t="s">
+      <c r="H100" s="37" t="s">
         <v>140</v>
       </c>
       <c r="I100" s="31"/>
@@ -5699,10 +5702,10 @@
       <c r="F101" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G101" s="35" t="s">
+      <c r="G101" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="H101" s="35" t="s">
+      <c r="H101" s="37" t="s">
         <v>140</v>
       </c>
       <c r="I101" s="31"/>
@@ -5731,10 +5734,10 @@
       <c r="F102" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G102" s="35" t="s">
+      <c r="G102" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="H102" s="35" t="s">
+      <c r="H102" s="37" t="s">
         <v>140</v>
       </c>
       <c r="I102" s="31"/>
@@ -5765,10 +5768,10 @@
       <c r="F103" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G103" s="35" t="s">
+      <c r="G103" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="H103" s="35" t="s">
+      <c r="H103" s="37" t="s">
         <v>140</v>
       </c>
       <c r="I103" s="31"/>
@@ -5828,10 +5831,10 @@
       <c r="F106" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G106" s="35" t="s">
+      <c r="G106" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="H106" s="35" t="s">
+      <c r="H106" s="37" t="s">
         <v>147</v>
       </c>
       <c r="I106" s="31"/>
@@ -5860,10 +5863,10 @@
       <c r="F107" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G107" s="35" t="s">
+      <c r="G107" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="H107" s="35" t="s">
+      <c r="H107" s="37" t="s">
         <v>147</v>
       </c>
       <c r="I107" s="31"/>
@@ -5894,10 +5897,10 @@
       <c r="F108" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G108" s="35" t="s">
+      <c r="G108" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="H108" s="35" t="s">
+      <c r="H108" s="37" t="s">
         <v>147</v>
       </c>
       <c r="I108" s="31"/>
@@ -5926,10 +5929,10 @@
       <c r="F109" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G109" s="35" t="s">
+      <c r="G109" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="H109" s="35" t="s">
+      <c r="H109" s="37" t="s">
         <v>147</v>
       </c>
       <c r="I109" s="31"/>
@@ -5960,10 +5963,10 @@
       <c r="F110" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G110" s="35" t="s">
+      <c r="G110" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="H110" s="35" t="s">
+      <c r="H110" s="37" t="s">
         <v>147</v>
       </c>
       <c r="I110" s="31"/>
@@ -5994,10 +5997,10 @@
       <c r="F111" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G111" s="35" t="s">
+      <c r="G111" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="H111" s="35" t="s">
+      <c r="H111" s="37" t="s">
         <v>147</v>
       </c>
       <c r="I111" s="31"/>
@@ -6026,10 +6029,10 @@
       <c r="F112" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G112" s="35" t="s">
+      <c r="G112" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="H112" s="35" t="s">
+      <c r="H112" s="37" t="s">
         <v>147</v>
       </c>
       <c r="I112" s="31"/>
@@ -6060,10 +6063,10 @@
       <c r="F113" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G113" s="35" t="s">
+      <c r="G113" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="H113" s="35" t="s">
+      <c r="H113" s="37" t="s">
         <v>147</v>
       </c>
       <c r="I113" s="31"/>
@@ -6123,10 +6126,10 @@
       <c r="F116" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G116" s="35" t="s">
+      <c r="G116" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="H116" s="35" t="s">
+      <c r="H116" s="37" t="s">
         <v>154</v>
       </c>
       <c r="I116" s="31"/>
@@ -6155,10 +6158,10 @@
       <c r="F117" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G117" s="35" t="s">
+      <c r="G117" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="H117" s="35" t="s">
+      <c r="H117" s="37" t="s">
         <v>154</v>
       </c>
       <c r="I117" s="31"/>
@@ -6189,10 +6192,10 @@
       <c r="F118" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G118" s="35" t="s">
+      <c r="G118" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="H118" s="35" t="s">
+      <c r="H118" s="37" t="s">
         <v>154</v>
       </c>
       <c r="I118" s="31"/>
@@ -6221,10 +6224,10 @@
       <c r="F119" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G119" s="35" t="s">
+      <c r="G119" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="H119" s="35" t="s">
+      <c r="H119" s="37" t="s">
         <v>154</v>
       </c>
       <c r="I119" s="31"/>
@@ -6255,10 +6258,10 @@
       <c r="F120" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G120" s="35" t="s">
+      <c r="G120" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="H120" s="35" t="s">
+      <c r="H120" s="37" t="s">
         <v>154</v>
       </c>
       <c r="I120" s="31"/>
@@ -6289,10 +6292,10 @@
       <c r="F121" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G121" s="35" t="s">
+      <c r="G121" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="H121" s="35" t="s">
+      <c r="H121" s="37" t="s">
         <v>154</v>
       </c>
       <c r="I121" s="31"/>
@@ -6352,10 +6355,10 @@
       <c r="F124" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G124" s="35" t="s">
+      <c r="G124" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="H124" s="35" t="s">
+      <c r="H124" s="37" t="s">
         <v>158</v>
       </c>
       <c r="I124" s="31"/>
@@ -6386,10 +6389,10 @@
       <c r="F125" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="G125" s="35" t="s">
+      <c r="G125" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="H125" s="35" t="s">
+      <c r="H125" s="37" t="s">
         <v>158</v>
       </c>
       <c r="I125" s="31"/>
@@ -6420,10 +6423,10 @@
       <c r="F126" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G126" s="35" t="s">
+      <c r="G126" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="H126" s="35" t="s">
+      <c r="H126" s="37" t="s">
         <v>158</v>
       </c>
       <c r="I126" s="31"/>
@@ -6571,10 +6574,10 @@
       <c r="F132" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G132" s="35" t="s">
+      <c r="G132" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="H132" s="35" t="s">
+      <c r="H132" s="37" t="s">
         <v>174</v>
       </c>
       <c r="I132" s="31"/>
@@ -6603,10 +6606,10 @@
       <c r="F133" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G133" s="35" t="s">
+      <c r="G133" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="H133" s="35" t="s">
+      <c r="H133" s="37" t="s">
         <v>174</v>
       </c>
       <c r="I133" s="31"/>
@@ -6637,10 +6640,10 @@
       <c r="F134" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G134" s="35" t="s">
+      <c r="G134" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="H134" s="35" t="s">
+      <c r="H134" s="37" t="s">
         <v>174</v>
       </c>
       <c r="I134" s="31"/>
@@ -6700,10 +6703,10 @@
       <c r="F137" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G137" s="35" t="s">
+      <c r="G137" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="H137" s="35" t="s">
+      <c r="H137" s="37" t="s">
         <v>182</v>
       </c>
       <c r="I137" s="31"/>
@@ -6734,10 +6737,10 @@
       <c r="F138" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G138" s="35" t="s">
+      <c r="G138" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="H138" s="35" t="s">
+      <c r="H138" s="37" t="s">
         <v>182</v>
       </c>
       <c r="I138" s="31"/>
@@ -6766,10 +6769,10 @@
       <c r="F139" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G139" s="35" t="s">
+      <c r="G139" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="H139" s="35" t="s">
+      <c r="H139" s="37" t="s">
         <v>182</v>
       </c>
       <c r="I139" s="31"/>
@@ -6800,10 +6803,10 @@
       <c r="F140" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G140" s="35" t="s">
+      <c r="G140" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="H140" s="35" t="s">
+      <c r="H140" s="37" t="s">
         <v>182</v>
       </c>
       <c r="I140" s="31"/>
@@ -6863,10 +6866,10 @@
       <c r="F143" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G143" s="35" t="s">
+      <c r="G143" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H143" s="35" t="s">
+      <c r="H143" s="37" t="s">
         <v>189</v>
       </c>
       <c r="I143" s="31"/>
@@ -6897,10 +6900,10 @@
       <c r="F144" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G144" s="35" t="s">
+      <c r="G144" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H144" s="35" t="s">
+      <c r="H144" s="37" t="s">
         <v>189</v>
       </c>
       <c r="I144" s="31"/>
@@ -6929,10 +6932,10 @@
       <c r="F145" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G145" s="35" t="s">
+      <c r="G145" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H145" s="35" t="s">
+      <c r="H145" s="37" t="s">
         <v>189</v>
       </c>
       <c r="I145" s="31"/>
@@ -6963,10 +6966,10 @@
       <c r="F146" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G146" s="35" t="s">
+      <c r="G146" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H146" s="35" t="s">
+      <c r="H146" s="37" t="s">
         <v>189</v>
       </c>
       <c r="I146" s="31"/>
@@ -7026,10 +7029,10 @@
       <c r="F149" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G149" s="35" t="s">
+      <c r="G149" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="H149" s="35" t="s">
+      <c r="H149" s="37" t="s">
         <v>196</v>
       </c>
       <c r="I149" s="31"/>
@@ -7060,10 +7063,10 @@
       <c r="F150" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G150" s="35" t="s">
+      <c r="G150" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="H150" s="35" t="s">
+      <c r="H150" s="37" t="s">
         <v>196</v>
       </c>
       <c r="I150" s="31"/>
@@ -7092,10 +7095,10 @@
       <c r="F151" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G151" s="35" t="s">
+      <c r="G151" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="H151" s="35" t="s">
+      <c r="H151" s="37" t="s">
         <v>196</v>
       </c>
       <c r="I151" s="31"/>
@@ -7126,10 +7129,10 @@
       <c r="F152" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G152" s="35" t="s">
+      <c r="G152" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="H152" s="35" t="s">
+      <c r="H152" s="37" t="s">
         <v>196</v>
       </c>
       <c r="I152" s="31"/>
@@ -7189,10 +7192,10 @@
       <c r="F155" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G155" s="35" t="s">
+      <c r="G155" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="H155" s="35" t="s">
+      <c r="H155" s="37" t="s">
         <v>203</v>
       </c>
       <c r="I155" s="31"/>
@@ -7223,10 +7226,10 @@
       <c r="F156" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G156" s="35" t="s">
+      <c r="G156" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="H156" s="35" t="s">
+      <c r="H156" s="37" t="s">
         <v>203</v>
       </c>
       <c r="I156" s="31"/>
@@ -7255,10 +7258,10 @@
       <c r="F157" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G157" s="35" t="s">
+      <c r="G157" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="H157" s="35" t="s">
+      <c r="H157" s="37" t="s">
         <v>203</v>
       </c>
       <c r="I157" s="31"/>
@@ -7289,10 +7292,10 @@
       <c r="F158" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G158" s="35" t="s">
+      <c r="G158" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="H158" s="35" t="s">
+      <c r="H158" s="37" t="s">
         <v>203</v>
       </c>
       <c r="I158" s="31"/>
@@ -7352,10 +7355,10 @@
       <c r="F161" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G161" s="35" t="s">
+      <c r="G161" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="H161" s="35" t="s">
+      <c r="H161" s="37" t="s">
         <v>210</v>
       </c>
       <c r="I161" s="31"/>
@@ -7386,10 +7389,10 @@
       <c r="F162" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G162" s="35" t="s">
+      <c r="G162" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="H162" s="35" t="s">
+      <c r="H162" s="37" t="s">
         <v>210</v>
       </c>
       <c r="I162" s="31"/>
@@ -7418,10 +7421,10 @@
       <c r="F163" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G163" s="35" t="s">
+      <c r="G163" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="H163" s="35" t="s">
+      <c r="H163" s="37" t="s">
         <v>210</v>
       </c>
       <c r="I163" s="31"/>
@@ -7452,10 +7455,10 @@
       <c r="F164" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G164" s="35" t="s">
+      <c r="G164" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="H164" s="35" t="s">
+      <c r="H164" s="37" t="s">
         <v>210</v>
       </c>
       <c r="I164" s="31"/>
@@ -7515,10 +7518,10 @@
       <c r="F167" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G167" s="35" t="s">
+      <c r="G167" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="H167" s="35" t="s">
+      <c r="H167" s="37" t="s">
         <v>217</v>
       </c>
       <c r="I167" s="31"/>
@@ -7549,10 +7552,10 @@
       <c r="F168" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G168" s="35" t="s">
+      <c r="G168" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="H168" s="35" t="s">
+      <c r="H168" s="37" t="s">
         <v>217</v>
       </c>
       <c r="I168" s="31"/>
@@ -7581,10 +7584,10 @@
       <c r="F169" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G169" s="35" t="s">
+      <c r="G169" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="H169" s="35" t="s">
+      <c r="H169" s="37" t="s">
         <v>217</v>
       </c>
       <c r="I169" s="31"/>
@@ -7615,10 +7618,10 @@
       <c r="F170" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G170" s="35" t="s">
+      <c r="G170" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="H170" s="35" t="s">
+      <c r="H170" s="37" t="s">
         <v>217</v>
       </c>
       <c r="I170" s="31"/>
@@ -7678,10 +7681,10 @@
       <c r="F173" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G173" s="35" t="s">
+      <c r="G173" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="H173" s="35" t="s">
+      <c r="H173" s="37" t="s">
         <v>224</v>
       </c>
       <c r="I173" s="31"/>
@@ -7712,10 +7715,10 @@
       <c r="F174" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G174" s="35" t="s">
+      <c r="G174" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="H174" s="35" t="s">
+      <c r="H174" s="37" t="s">
         <v>224</v>
       </c>
       <c r="I174" s="31"/>
@@ -7744,10 +7747,10 @@
       <c r="F175" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G175" s="35" t="s">
+      <c r="G175" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="H175" s="35" t="s">
+      <c r="H175" s="37" t="s">
         <v>224</v>
       </c>
       <c r="I175" s="31"/>
@@ -7778,10 +7781,10 @@
       <c r="F176" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G176" s="35" t="s">
+      <c r="G176" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="H176" s="35" t="s">
+      <c r="H176" s="37" t="s">
         <v>224</v>
       </c>
       <c r="I176" s="31"/>
@@ -7841,14 +7844,14 @@
       <c r="F179" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G179" s="35" t="s">
+      <c r="G179" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="H179" s="35" t="s">
+      <c r="H179" s="37" t="s">
         <v>231</v>
       </c>
       <c r="I179" s="31"/>
-      <c r="J179" s="33" t="s">
+      <c r="J179" s="36" t="s">
         <v>227</v>
       </c>
       <c r="K179" s="31"/>
@@ -7875,14 +7878,14 @@
       <c r="F180" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G180" s="35" t="s">
+      <c r="G180" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="H180" s="35" t="s">
+      <c r="H180" s="37" t="s">
         <v>231</v>
       </c>
       <c r="I180" s="31"/>
-      <c r="J180" s="33" t="s">
+      <c r="J180" s="36" t="s">
         <v>232</v>
       </c>
       <c r="K180" s="31"/>
@@ -7907,10 +7910,10 @@
       <c r="F181" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G181" s="35" t="s">
+      <c r="G181" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="H181" s="35" t="s">
+      <c r="H181" s="37" t="s">
         <v>231</v>
       </c>
       <c r="I181" s="31"/>
@@ -7941,10 +7944,10 @@
       <c r="F182" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G182" s="35" t="s">
+      <c r="G182" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="H182" s="35" t="s">
+      <c r="H182" s="37" t="s">
         <v>231</v>
       </c>
       <c r="I182" s="31"/>
@@ -8004,10 +8007,10 @@
       <c r="F185" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G185" s="35" t="s">
+      <c r="G185" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="H185" s="35" t="s">
+      <c r="H185" s="37" t="s">
         <v>237</v>
       </c>
       <c r="I185" s="31"/>
@@ -8038,10 +8041,10 @@
       <c r="F186" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G186" s="35" t="s">
+      <c r="G186" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="H186" s="35" t="s">
+      <c r="H186" s="37" t="s">
         <v>237</v>
       </c>
       <c r="I186" s="31"/>
@@ -8072,10 +8075,10 @@
       <c r="F187" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G187" s="35" t="s">
+      <c r="G187" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="H187" s="35" t="s">
+      <c r="H187" s="37" t="s">
         <v>237</v>
       </c>
       <c r="I187" s="31"/>
@@ -8106,10 +8109,10 @@
       <c r="F188" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="G188" s="35" t="s">
+      <c r="G188" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="H188" s="35" t="s">
+      <c r="H188" s="37" t="s">
         <v>237</v>
       </c>
       <c r="I188" s="31"/>
@@ -8169,10 +8172,10 @@
       <c r="F191" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G191" s="35" t="s">
+      <c r="G191" s="37" t="s">
         <v>245</v>
       </c>
-      <c r="H191" s="35" t="s">
+      <c r="H191" s="37" t="s">
         <v>246</v>
       </c>
       <c r="I191" s="31"/>
@@ -8203,10 +8206,10 @@
       <c r="F192" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="G192" s="35" t="s">
+      <c r="G192" s="37" t="s">
         <v>245</v>
       </c>
-      <c r="H192" s="35" t="s">
+      <c r="H192" s="37" t="s">
         <v>246</v>
       </c>
       <c r="I192" s="31"/>
@@ -8237,10 +8240,10 @@
       <c r="F193" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="G193" s="35" t="s">
+      <c r="G193" s="37" t="s">
         <v>245</v>
       </c>
-      <c r="H193" s="35" t="s">
+      <c r="H193" s="37" t="s">
         <v>246</v>
       </c>
       <c r="I193" s="31"/>
@@ -8271,10 +8274,10 @@
       <c r="F194" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G194" s="35" t="s">
+      <c r="G194" s="37" t="s">
         <v>245</v>
       </c>
-      <c r="H194" s="35" t="s">
+      <c r="H194" s="37" t="s">
         <v>246</v>
       </c>
       <c r="I194" s="31"/>
@@ -8396,10 +8399,10 @@
       <c r="F199" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G199" s="35" t="s">
+      <c r="G199" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="H199" s="35" t="s">
+      <c r="H199" s="37" t="s">
         <v>256</v>
       </c>
       <c r="I199" s="31"/>
@@ -8430,10 +8433,10 @@
       <c r="F200" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G200" s="35" t="s">
+      <c r="G200" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="H200" s="35" t="s">
+      <c r="H200" s="37" t="s">
         <v>256</v>
       </c>
       <c r="I200" s="31"/>
@@ -8531,10 +8534,10 @@
       <c r="F204" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G204" s="35" t="s">
+      <c r="G204" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="H204" s="35" t="s">
+      <c r="H204" s="37" t="s">
         <v>265</v>
       </c>
       <c r="I204" s="31"/>
@@ -8565,10 +8568,10 @@
       <c r="F205" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G205" s="35" t="s">
+      <c r="G205" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="H205" s="35" t="s">
+      <c r="H205" s="37" t="s">
         <v>265</v>
       </c>
       <c r="I205" s="31"/>
@@ -8666,10 +8669,10 @@
       <c r="F209" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G209" s="35" t="s">
+      <c r="G209" s="37" t="s">
         <v>277</v>
       </c>
-      <c r="H209" s="35" t="s">
+      <c r="H209" s="37" t="s">
         <v>273</v>
       </c>
       <c r="I209" s="31"/>
@@ -8700,10 +8703,10 @@
       <c r="F210" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G210" s="35" t="s">
+      <c r="G210" s="37" t="s">
         <v>277</v>
       </c>
-      <c r="H210" s="35" t="s">
+      <c r="H210" s="37" t="s">
         <v>273</v>
       </c>
       <c r="I210" s="31"/>
@@ -8801,10 +8804,10 @@
       <c r="F214" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G214" s="35" t="s">
+      <c r="G214" s="37" t="s">
         <v>285</v>
       </c>
-      <c r="H214" s="35" t="s">
+      <c r="H214" s="37" t="s">
         <v>282</v>
       </c>
       <c r="I214" s="31"/>
@@ -8835,10 +8838,10 @@
       <c r="F215" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G215" s="35" t="s">
+      <c r="G215" s="37" t="s">
         <v>285</v>
       </c>
-      <c r="H215" s="35" t="s">
+      <c r="H215" s="37" t="s">
         <v>282</v>
       </c>
       <c r="I215" s="31"/>
@@ -9035,10 +9038,10 @@
       <c r="F223" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G223" s="35" t="s">
+      <c r="G223" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="H223" s="35" t="s">
+      <c r="H223" s="37" t="s">
         <v>297</v>
       </c>
       <c r="I223" s="31"/>
@@ -9069,10 +9072,10 @@
       <c r="F224" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G224" s="35" t="s">
+      <c r="G224" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="H224" s="35" t="s">
+      <c r="H224" s="37" t="s">
         <v>297</v>
       </c>
       <c r="I224" s="31"/>
@@ -9170,10 +9173,10 @@
       <c r="F228" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G228" s="35" t="s">
+      <c r="G228" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="H228" s="35" t="s">
+      <c r="H228" s="37" t="s">
         <v>304</v>
       </c>
       <c r="I228" s="31"/>
@@ -9204,10 +9207,10 @@
       <c r="F229" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G229" s="35" t="s">
+      <c r="G229" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="H229" s="35" t="s">
+      <c r="H229" s="37" t="s">
         <v>304</v>
       </c>
       <c r="I229" s="31"/>
@@ -9305,10 +9308,10 @@
       <c r="F233" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G233" s="35" t="s">
+      <c r="G233" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H233" s="35" t="s">
+      <c r="H233" s="37" t="s">
         <v>313</v>
       </c>
       <c r="I233" s="31"/>
@@ -9339,10 +9342,10 @@
       <c r="F234" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G234" s="35" t="s">
+      <c r="G234" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H234" s="35" t="s">
+      <c r="H234" s="37" t="s">
         <v>313</v>
       </c>
       <c r="I234" s="31"/>
@@ -9539,10 +9542,10 @@
       <c r="F242" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G242" s="35" t="s">
+      <c r="G242" s="37" t="s">
         <v>332</v>
       </c>
-      <c r="H242" s="35" t="s">
+      <c r="H242" s="37" t="s">
         <v>328</v>
       </c>
       <c r="I242" s="31"/>
@@ -9573,10 +9576,10 @@
       <c r="F243" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G243" s="35" t="s">
+      <c r="G243" s="37" t="s">
         <v>332</v>
       </c>
-      <c r="H243" s="35" t="s">
+      <c r="H243" s="37" t="s">
         <v>328</v>
       </c>
       <c r="I243" s="31"/>
@@ -9674,10 +9677,10 @@
       <c r="F247" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G247" s="35" t="s">
+      <c r="G247" s="37" t="s">
         <v>340</v>
       </c>
-      <c r="H247" s="35" t="s">
+      <c r="H247" s="37" t="s">
         <v>336</v>
       </c>
       <c r="I247" s="31"/>
@@ -9708,10 +9711,10 @@
       <c r="F248" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G248" s="35" t="s">
+      <c r="G248" s="37" t="s">
         <v>340</v>
       </c>
-      <c r="H248" s="35" t="s">
+      <c r="H248" s="37" t="s">
         <v>336</v>
       </c>
       <c r="I248" s="31"/>
@@ -9908,10 +9911,10 @@
       <c r="F256" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G256" s="35" t="s">
+      <c r="G256" s="37" t="s">
         <v>355</v>
       </c>
-      <c r="H256" s="35" t="s">
+      <c r="H256" s="37" t="s">
         <v>351</v>
       </c>
       <c r="I256" s="31"/>
@@ -9942,10 +9945,10 @@
       <c r="F257" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G257" s="35" t="s">
+      <c r="G257" s="37" t="s">
         <v>355</v>
       </c>
-      <c r="H257" s="35" t="s">
+      <c r="H257" s="37" t="s">
         <v>351</v>
       </c>
       <c r="I257" s="31"/>
@@ -10043,10 +10046,10 @@
       <c r="F261" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G261" s="35" t="s">
+      <c r="G261" s="37" t="s">
         <v>362</v>
       </c>
-      <c r="H261" s="35" t="s">
+      <c r="H261" s="37" t="s">
         <v>359</v>
       </c>
       <c r="I261" s="31"/>
@@ -10077,10 +10080,10 @@
       <c r="F262" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G262" s="35" t="s">
+      <c r="G262" s="37" t="s">
         <v>362</v>
       </c>
-      <c r="H262" s="35" t="s">
+      <c r="H262" s="37" t="s">
         <v>359</v>
       </c>
       <c r="I262" s="31"/>
@@ -10178,10 +10181,10 @@
       <c r="F266" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G266" s="35" t="s">
+      <c r="G266" s="37" t="s">
         <v>368</v>
       </c>
-      <c r="H266" s="35" t="s">
+      <c r="H266" s="37" t="s">
         <v>365</v>
       </c>
       <c r="I266" s="31"/>
@@ -10212,10 +10215,10 @@
       <c r="F267" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G267" s="35" t="s">
+      <c r="G267" s="37" t="s">
         <v>368</v>
       </c>
-      <c r="H267" s="35" t="s">
+      <c r="H267" s="37" t="s">
         <v>365</v>
       </c>
       <c r="I267" s="31"/>
